--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/group_pdf_bins_pet.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/group_pdf_bins_pet.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -169,7 +170,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.58499999999999996</v>
+        <v>0.58499999999999997</v>
       </c>
     </row>
     <row r="22">
@@ -244,12 +245,12 @@
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>1.0350000000000001</v>
+        <v>1.0350000000000002</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>1.0649999999999999</v>
+        <v>1.065</v>
       </c>
     </row>
     <row r="38">
@@ -354,7 +355,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.6949999999999998</v>
+        <v>1.6949999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -374,7 +375,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.8149999999999999</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="63">
@@ -499,7 +500,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>2.5649999999999999</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="88">
@@ -514,7 +515,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>2.6550000000000002</v>
+        <v>2.6550000000000003</v>
       </c>
     </row>
     <row r="91">
